--- a/data/gravel/KOGA Colmaro Extreme 2025.xlsx
+++ b/data/gravel/KOGA Colmaro Extreme 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2A64E8-D1A2-9C4A-AF86-03CA0A29995F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86A9DC4-F398-2246-841F-C002BA6F0C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11920" yWindow="1200" windowWidth="25600" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="-26520" windowWidth="28960" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -254,15 +254,9 @@
     <t>yes</t>
   </si>
   <si>
-    <t>KOGA</t>
-  </si>
-  <si>
     <t>Colmaro Extreme</t>
   </si>
   <si>
-    <t>Size</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -275,39 +269,6 @@
     <t>XL</t>
   </si>
   <si>
-    <t>Top Tube (T/T)</t>
-  </si>
-  <si>
-    <t>Chainstay (C/S)</t>
-  </si>
-  <si>
-    <t>Wheelbase (WB)</t>
-  </si>
-  <si>
-    <t>Bottom Bracket Drop (BB)</t>
-  </si>
-  <si>
-    <t>Rake (RA)</t>
-  </si>
-  <si>
-    <t>Head Tube Angle (H/Tº)</t>
-  </si>
-  <si>
-    <t>Seat Tube Angle (S/Tº)</t>
-  </si>
-  <si>
-    <t>Trail (TR)</t>
-  </si>
-  <si>
-    <t>Head Tube Length (H/T)</t>
-  </si>
-  <si>
-    <t>Reach (RE)</t>
-  </si>
-  <si>
-    <t>Stack (ST)</t>
-  </si>
-  <si>
     <t>trail</t>
   </si>
   <si>
@@ -323,7 +284,97 @@
     <t>DKK</t>
   </si>
   <si>
-    <t>a8:f32</t>
+    <t>XS</t>
+  </si>
+  <si>
+    <t>Stack (mm)</t>
+  </si>
+  <si>
+    <t>Reach (mm)</t>
+  </si>
+  <si>
+    <t>Stack to Reach Ratio</t>
+  </si>
+  <si>
+    <t>1.48:1</t>
+  </si>
+  <si>
+    <t>1.5:1</t>
+  </si>
+  <si>
+    <t>1.52:1</t>
+  </si>
+  <si>
+    <t>Seat Tube Length, C-T (mm)</t>
+  </si>
+  <si>
+    <t>Top Tube Slope (deg)</t>
+  </si>
+  <si>
+    <t>Head Tube Angle (deg)</t>
+  </si>
+  <si>
+    <t>Seat Tube Angle (deg)</t>
+  </si>
+  <si>
+    <t>Head Tube Length (mm)</t>
+  </si>
+  <si>
+    <t>Bottom Bracket Drop (mm)</t>
+  </si>
+  <si>
+    <t>Bottom Bracket Height (mm)</t>
+  </si>
+  <si>
+    <t>Chainstay Length (mm)</t>
+  </si>
+  <si>
+    <t>Chainstay Length Horizontal (mm)</t>
+  </si>
+  <si>
+    <t>Front-Center (mm)</t>
+  </si>
+  <si>
+    <t>Front-Center Horizontal (mm)</t>
+  </si>
+  <si>
+    <t>Wheelbase (mm)</t>
+  </si>
+  <si>
+    <t>Fork Offset/Rake (mm)</t>
+  </si>
+  <si>
+    <t>https://bikeinsights.com/bikes/604f6e0bd0deb400177ce61f-koga-colmaro?version=2025&amp;build=extreme</t>
+  </si>
+  <si>
+    <t>1.49:1</t>
+  </si>
+  <si>
+    <t>1.47:1</t>
+  </si>
+  <si>
+    <t>frame size</t>
+  </si>
+  <si>
+    <t>stack_to_reach</t>
+  </si>
+  <si>
+    <t>top_tube_slope_spec</t>
+  </si>
+  <si>
+    <t>bb_height</t>
+  </si>
+  <si>
+    <t>chainstay_horiz</t>
+  </si>
+  <si>
+    <t>front_center_horiz</t>
+  </si>
+  <si>
+    <t>a8:g37</t>
+  </si>
+  <si>
+    <t>Koga</t>
   </si>
 </sst>
 </file>
@@ -663,29 +714,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -693,160 +744,202 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>45930</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
         <v>75</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>76</v>
       </c>
-      <c r="D8" t="s">
+      <c r="G8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C9">
-        <v>544</v>
+        <v>566</v>
       </c>
       <c r="D9">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="E9">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="F9">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+      <c r="G9">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C10">
-        <v>435</v>
+        <v>380</v>
       </c>
       <c r="D10">
-        <v>435</v>
+        <v>390</v>
       </c>
       <c r="E10">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="F10">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>12</v>
+        <v>405</v>
+      </c>
+      <c r="G10">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C11">
-        <v>1020</v>
+        <f>VALUE(LEFT(H11,4))</f>
+        <v>1.49</v>
       </c>
       <c r="D11">
-        <v>1028</v>
+        <f t="shared" ref="D11:G11" si="0">VALUE(LEFT(I11,4))</f>
+        <v>1.48</v>
       </c>
       <c r="E11">
-        <v>1047</v>
+        <f t="shared" si="0"/>
+        <v>1.47</v>
       </c>
       <c r="F11">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <f>VALUE(LEFT(K11,3))</f>
+        <v>1.5</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>1.52</v>
+      </c>
+      <c r="H11" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C12">
-        <v>75</v>
+        <v>470</v>
       </c>
       <c r="D12">
-        <v>75</v>
+        <v>490</v>
       </c>
       <c r="E12">
-        <v>75</v>
+        <v>520</v>
       </c>
       <c r="F12">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>20</v>
+        <v>550</v>
+      </c>
+      <c r="G12">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C13">
-        <v>45</v>
+        <v>12.7</v>
       </c>
       <c r="D13">
-        <v>45</v>
+        <v>11.5</v>
       </c>
       <c r="E13">
-        <v>45</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="F13">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8.4</v>
+      </c>
+      <c r="G13">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C14">
-        <v>70.5</v>
+        <v>70</v>
       </c>
       <c r="D14">
         <v>71</v>
@@ -855,481 +948,664 @@
         <v>71</v>
       </c>
       <c r="F14">
-        <v>71.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="G14">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C15">
-        <v>73</v>
+        <v>73.5</v>
       </c>
       <c r="D15">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="E15">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="F15">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>73.5</v>
+      </c>
+      <c r="G15">
+        <v>73.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C16">
-        <v>71.599999999999994</v>
+        <v>100</v>
       </c>
       <c r="D16">
-        <v>68.5</v>
+        <v>110</v>
       </c>
       <c r="E16">
-        <v>68.5</v>
+        <v>120</v>
       </c>
       <c r="F16">
-        <v>65.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="G16">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C17">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="D17">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="E17">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="F17">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>18</v>
+        <v>75</v>
+      </c>
+      <c r="G17">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C18">
-        <v>376</v>
+        <v>286</v>
       </c>
       <c r="D18">
-        <v>378</v>
+        <v>286</v>
       </c>
       <c r="E18">
-        <v>388</v>
+        <v>286</v>
       </c>
       <c r="F18">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+      <c r="G18">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C19">
-        <v>547</v>
+        <v>442</v>
       </c>
       <c r="D19">
-        <v>577</v>
+        <v>442</v>
       </c>
       <c r="E19">
-        <v>605</v>
+        <v>442</v>
       </c>
       <c r="F19">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+      <c r="G19">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20">
+        <v>435.6</v>
+      </c>
+      <c r="D20">
+        <v>435.6</v>
+      </c>
+      <c r="E20">
+        <v>435.6</v>
+      </c>
+      <c r="F20">
+        <v>435.6</v>
+      </c>
+      <c r="G20">
+        <v>435.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21">
+        <v>613</v>
+      </c>
+      <c r="D21">
+        <v>622</v>
+      </c>
+      <c r="E21">
+        <v>636.79999999999995</v>
+      </c>
+      <c r="F21">
+        <v>641.79999999999995</v>
+      </c>
+      <c r="G21">
+        <v>652.70000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22">
+        <v>608.4</v>
+      </c>
+      <c r="D22">
+        <v>617.4</v>
+      </c>
+      <c r="E22">
+        <v>632.4</v>
+      </c>
+      <c r="F22">
+        <v>637.4</v>
+      </c>
+      <c r="G22">
+        <v>648.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23">
+        <v>1044</v>
+      </c>
+      <c r="D23">
+        <v>1053</v>
+      </c>
+      <c r="E23">
+        <v>1068</v>
+      </c>
+      <c r="F23">
+        <v>1073</v>
+      </c>
+      <c r="G23">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24">
+        <v>51</v>
+      </c>
+      <c r="D24">
+        <v>51</v>
+      </c>
+      <c r="E24">
+        <v>51</v>
+      </c>
+      <c r="F24">
+        <v>51</v>
+      </c>
+      <c r="G24">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>19</v>
       </c>
-      <c r="C23">
+      <c r="C28">
         <v>436</v>
       </c>
-      <c r="D23">
+      <c r="D28">
         <v>436</v>
       </c>
-      <c r="E23">
+      <c r="E28">
         <v>436</v>
       </c>
-      <c r="F23">
+      <c r="F28">
         <v>436</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="G28">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>25</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C28">
+      <c r="C33">
         <v>700</v>
       </c>
-      <c r="D28">
+      <c r="D33">
         <v>700</v>
       </c>
-      <c r="E28">
+      <c r="E33">
         <v>700</v>
       </c>
-      <c r="F28">
+      <c r="F33">
         <v>700</v>
       </c>
-      <c r="H28">
+      <c r="G33">
         <v>700</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>26</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B34" t="s">
         <v>26</v>
       </c>
-      <c r="C29">
+      <c r="C34">
         <v>50</v>
       </c>
-      <c r="D29">
+      <c r="D34">
         <v>50</v>
       </c>
-      <c r="E29">
+      <c r="E34">
         <v>50</v>
       </c>
-      <c r="F29">
+      <c r="F34">
         <v>50</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="G34">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>27</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B35" t="s">
         <v>27</v>
       </c>
-      <c r="C30">
+      <c r="C35">
         <v>50</v>
       </c>
-      <c r="D30">
+      <c r="D35">
         <v>50</v>
       </c>
-      <c r="E30">
+      <c r="E35">
         <v>50</v>
       </c>
-      <c r="F30">
+      <c r="F35">
         <v>50</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="G35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>28</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B36" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="C36">
+        <v>150</v>
+      </c>
+      <c r="D36">
+        <v>159</v>
+      </c>
+      <c r="E36">
+        <v>171</v>
+      </c>
+      <c r="F36">
+        <v>180</v>
+      </c>
+      <c r="G36">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B37" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="C37">
+        <v>158</v>
+      </c>
+      <c r="D37">
+        <v>170</v>
+      </c>
+      <c r="E37">
+        <v>179</v>
+      </c>
+      <c r="F37">
+        <v>188</v>
+      </c>
+      <c r="G37">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>30</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B39" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>67</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B40" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>69</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B41" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="B42" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="B43" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="2"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>35</v>
       </c>
-      <c r="B41">
+      <c r="B46">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>37</v>
       </c>
-      <c r="B43">
+      <c r="B48">
         <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48">
-        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="B49">
+        <v>40</v>
+      </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51">
-        <v>27.2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>72</v>
+        <v>41</v>
+      </c>
+      <c r="B52">
+        <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="B53">
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B54" s="2"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>45</v>
+      </c>
+      <c r="B56">
+        <v>27.2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
-      </c>
-      <c r="B58" s="2"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B63" s="2"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
-      </c>
-      <c r="B66" s="2"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>58</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70">
-        <v>19999</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B71" s="2"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>61</v>
+      </c>
+      <c r="B72" s="2"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75">
+        <v>19999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>66</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>95</v>
+      <c r="B77" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/KOGA Colmaro Extreme 2025.xlsx
+++ b/data/gravel/KOGA Colmaro Extreme 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86A9DC4-F398-2246-841F-C002BA6F0C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98D7B2D-9318-554B-BAE0-E9EB9BFAD53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="-26520" windowWidth="28960" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8100" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>Koga</t>
+  </si>
+  <si>
+    <t>https://www.koga.com/bike-images/KCDE2006.tif?width=1500&amp;format=jpg</t>
   </si>
 </sst>
 </file>
@@ -759,10 +762,13 @@
       <c r="B5" t="s">
         <v>81</v>
       </c>
+      <c r="H5" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">

--- a/data/gravel/KOGA Colmaro Extreme 2025.xlsx
+++ b/data/gravel/KOGA Colmaro Extreme 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98D7B2D-9318-554B-BAE0-E9EB9BFAD53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D19E474-13F8-E646-92AA-B8774D2B1E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8100" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -378,6 +378,12 @@
   </si>
   <si>
     <t>https://www.koga.com/bike-images/KCDE2006.tif?width=1500&amp;format=jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Heerenveen, Netherlands</t>
   </si>
 </sst>
 </file>
@@ -717,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1614,6 +1620,14 @@
         <v>82</v>
       </c>
     </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>115</v>
+      </c>
+      <c r="B78" t="s">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/KOGA Colmaro Extreme 2025.xlsx
+++ b/data/gravel/KOGA Colmaro Extreme 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D19E474-13F8-E646-92AA-B8774D2B1E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590C1A86-12D3-7D42-A5CC-F08E5761A648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -384,6 +384,24 @@
   </si>
   <si>
     <t>Heerenveen, Netherlands</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -723,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1474,157 +1492,187 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="2"/>
+        <v>117</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56">
-        <v>27.2</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>46</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>49</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B60" s="2"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B62">
+        <v>27.2</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>52</v>
-      </c>
-      <c r="B63" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>57</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>58</v>
-      </c>
-      <c r="B69">
-        <v>1</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B69" s="2"/>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>60</v>
-      </c>
-      <c r="B71" s="2"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>61</v>
-      </c>
-      <c r="B72" s="2"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>62</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>72</v>
+        <v>56</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B75">
-        <v>19999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>66</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>82</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B77" s="2"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" s="2"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>64</v>
+      </c>
+      <c r="B81">
+        <v>19999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>66</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>115</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B84" t="s">
         <v>116</v>
       </c>
     </row>
